--- a/outils/tenue-livres-placements/Sortie_Client_Exemple_données_fictives_2025.xlsx
+++ b/outils/tenue-livres-placements/Sortie_Client_Exemple_données_fictives_2025.xlsx
@@ -9,15 +9,16 @@
   <sheets>
     <sheet name="Sommaire" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Alertes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dispositions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Revenus" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Frais" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Positions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Journal" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Rapprochement relevés" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Rapprochement 1099" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="T1135" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Taux" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Par titre" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dispositions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Revenus" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Frais" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Positions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Journal" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Rapprochement relevés" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Rapprochement 1099" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="T1135" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Taux" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -95,12 +96,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -554,7 +555,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-21 11:45</t>
+          <t>2026-09-21 11:48</t>
         </is>
       </c>
     </row>
@@ -735,6 +736,530 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Année</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Élément</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Selon 1099</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Calculé (USD)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Écart</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RCM-1001</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Dividendes bruts USD</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>318</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>318</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RCM-1001</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Impôt étranger retenu USD</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RCM-1001</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Intérêts USD</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>310.25</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>310.25</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RCM-1001</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Produits de disposition USD</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>11390.05</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>11390.05</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RCM-1002</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Dividendes bruts USD</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RCM-1002</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Impôt étranger retenu USD</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RCM-1002</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Intérêts USD</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RCM-1002</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Produits de disposition USD</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RCM-1001</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dividendes bruts USD</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RCM-1001</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Impôt étranger retenu USD</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RCM-1001</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Intérêts USD</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RCM-1001</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Produits de disposition USD</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>49480.1</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>49480.1</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RCM-1002</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dividendes bruts USD</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RCM-1002</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Impôt étranger retenu USD</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RCM-1002</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Intérêts USD</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RCM-1002</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Produits de disposition USD</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>44990.05</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>44990.05</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -916,16 +1441,16 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="5" t="n">
         <v>440581.53</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="5" t="n">
         <v>326190.33</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="5" t="n">
         <v>1207.26</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="5" t="n">
         <v>16036.28</v>
       </c>
     </row>
@@ -934,7 +1459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -972,253 +1497,253 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="6" t="n">
         <v>45356</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>45356</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="8" t="n">
         <v>1.388</v>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="6" t="n">
         <v>45366</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>45366</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="8" t="n">
         <v>1.3951</v>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>45414</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>45414</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="8" t="n">
         <v>1.3516</v>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>45453</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>45453</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>1.3144</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>45471</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>45471</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>1.3162</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>45555</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>45555</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>1.3711</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>45657</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>45657</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>1.415</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="6" t="n">
         <v>45667</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>45667</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>1.3937</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>45702</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>45702</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>1.3843</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="6" t="n">
         <v>45719</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>45719</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>1.3496</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>45736</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>45736</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="8" t="n">
         <v>1.3502</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="6" t="n">
         <v>45748</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>45748</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="8" t="n">
         <v>1.3444</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="6" t="n">
         <v>45792</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>45792</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="8" t="n">
         <v>1.3222</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="6" t="n">
         <v>45835</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>45835</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="8" t="n">
         <v>1.3329</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="6" t="n">
         <v>45853</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>45853</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="8" t="n">
         <v>1.3272</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="6" t="n">
         <v>45881</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>45881</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="8" t="n">
         <v>1.3697</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="6" t="n">
         <v>45930</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>45930</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="8" t="n">
         <v>1.4117</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="6" t="n">
         <v>45936</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>45936</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="8" t="n">
         <v>1.4123</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="6" t="n">
         <v>45964</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>45964</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="8" t="n">
         <v>1.4067</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="6" t="n">
         <v>45975</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>45975</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="8" t="n">
         <v>1.4204</v>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="6" t="n">
         <v>46022</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>46022</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="8" t="n">
         <v>1.3929</v>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1316,6 +1841,351 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Revenus, retenues et gains par placement pour 2025 (CAD et USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Titre</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Dividendes CAD</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Dividendes USD</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Intérêts CAD</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Intérêts USD</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Remb. de capital CAD</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Remb. de capital USD</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Impôt étranger retenu CAD</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Impôt étranger retenu USD</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Nb de dispositions</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Gain (perte) en capital CAD</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Gain (perte) USD (indicatif)</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Perte apparente refusée CAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>125.77</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>5837.92</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>3990.05</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ENCAISSE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Encaisse USD au début du suivi</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>574.99</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>-1982.58</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>-2519.9</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>2973.86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Vanguard Total Stock Market ETF</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>506.5</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>75.98</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>12180.94</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>6186.96</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="5" t="n">
+        <v>632.27</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>469.5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>574.99</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>105.93</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>78.23</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>16036.28</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>7657.11</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>2973.86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1431,7 +2301,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="6" t="n">
         <v>45719</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1444,7 +2314,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="7" t="n">
         <v>100</v>
       </c>
       <c r="E2" s="4" t="n">
@@ -1456,7 +2326,7 @@
       <c r="G2" s="4" t="n">
         <v>37990.05</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="H2" s="8" t="n">
         <v>1.3496</v>
       </c>
       <c r="I2" s="4" t="n">
@@ -1492,7 +2362,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="6" t="n">
         <v>45881</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1505,7 +2375,7 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>100</v>
       </c>
       <c r="E3" s="4" t="n">
@@ -1517,7 +2387,7 @@
       <c r="G3" s="4" t="n">
         <v>11490.05</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="8" t="n">
         <v>1.3697</v>
       </c>
       <c r="I3" s="4" t="n">
@@ -1549,7 +2419,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>45936</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1562,7 +2432,7 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>150</v>
       </c>
       <c r="E4" s="4" t="n">
@@ -1574,7 +2444,7 @@
       <c r="G4" s="4" t="n">
         <v>44990.05</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="8" t="n">
         <v>1.4123</v>
       </c>
       <c r="I4" s="4" t="n">
@@ -1614,7 +2484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1700,7 +2570,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="6" t="n">
         <v>45702</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1727,7 +2597,7 @@
       <c r="G2" s="4" t="n">
         <v>31.87</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="H2" s="8" t="n">
         <v>1.3843</v>
       </c>
       <c r="I2" s="4" t="n">
@@ -1744,7 +2614,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="6" t="n">
         <v>45792</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1771,7 +2641,7 @@
       <c r="G3" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="8" t="n">
         <v>1.3222</v>
       </c>
       <c r="I3" s="4" t="n">
@@ -1792,7 +2662,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>45835</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1819,7 +2689,7 @@
       <c r="G4" s="4" t="n">
         <v>161.5</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="8" t="n">
         <v>1.3329</v>
       </c>
       <c r="I4" s="4" t="n">
@@ -1836,7 +2706,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>45835</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1863,7 +2733,7 @@
       <c r="G5" s="4" t="n">
         <v>161.5</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="8" t="n">
         <v>1.3329</v>
       </c>
       <c r="I5" s="4" t="n">
@@ -1880,7 +2750,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>45975</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1907,7 +2777,7 @@
       <c r="G6" s="4" t="n">
         <v>36.4</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="8" t="n">
         <v>1.4204</v>
       </c>
       <c r="I6" s="4" t="n">
@@ -1928,7 +2798,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>46022</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1955,7 +2825,7 @@
       <c r="G7" s="4" t="n">
         <v>412.8</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="8" t="n">
         <v>1.3929</v>
       </c>
       <c r="I7" s="4" t="n">
@@ -2111,7 +2981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2167,7 +3037,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="6" t="n">
         <v>45667</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -2178,7 +3048,7 @@
       <c r="C2" s="4" t="n">
         <v>1250</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="8" t="n">
         <v>1.3937</v>
       </c>
       <c r="E2" s="4" t="n">
@@ -2196,7 +3066,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2269,7 +3139,7 @@
           <t>Apple Inc.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <v>200</v>
       </c>
       <c r="D4" s="4" t="n">
@@ -2296,7 +3166,7 @@
           <t>Microsoft Corp.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>60</v>
       </c>
       <c r="D5" s="4" t="n">
@@ -2323,7 +3193,7 @@
           <t>Vanguard Total Stock Market ETF</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>250</v>
       </c>
       <c r="D6" s="4" t="n">
@@ -2384,7 +3254,7 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>200</v>
       </c>
       <c r="D11" s="4" t="n">
@@ -2405,7 +3275,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>60</v>
       </c>
       <c r="D12" s="4" t="n">
@@ -2426,7 +3296,7 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>200</v>
       </c>
       <c r="D13" s="4" t="n">
@@ -2447,7 +3317,7 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>94258.42</v>
       </c>
       <c r="D14" s="4" t="n">
@@ -2468,7 +3338,7 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <v>50</v>
       </c>
       <c r="D15" s="4" t="n">
@@ -2489,7 +3359,7 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>39718.1</v>
       </c>
       <c r="D16" s="4" t="n">
@@ -2504,7 +3374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2626,7 +3496,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="6" t="n">
         <v>45293</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -2647,7 +3517,7 @@
       <c r="G2" s="4" t="n">
         <v>135000</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="L2" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M2" s="4" t="n">
@@ -2674,7 +3544,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="6" t="n">
         <v>45293</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -2692,7 +3562,7 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>200</v>
       </c>
       <c r="G3" s="4" t="n">
@@ -2701,7 +3571,7 @@
       <c r="K3" s="4" t="n">
         <v>39600</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="L3" s="7" t="n">
         <v>200</v>
       </c>
       <c r="M3" s="4" t="n">
@@ -2728,7 +3598,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>45293</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -2749,7 +3619,7 @@
       <c r="G4" s="4" t="n">
         <v>30000</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="4" t="n">
@@ -2772,7 +3642,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>45356</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -2790,7 +3660,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>100</v>
       </c>
       <c r="F5" s="4" t="n">
@@ -2802,13 +3672,13 @@
       <c r="H5" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J5" s="8" t="n">
         <v>1.388</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>56227.81</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="7" t="n">
         <v>100</v>
       </c>
       <c r="M5" s="4" t="n">
@@ -2831,7 +3701,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>45366</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -2855,13 +3725,13 @@
       <c r="I6" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="8" t="n">
         <v>1.3951</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>66.95999999999999</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="7" t="n">
         <v>200</v>
       </c>
       <c r="M6" s="4" t="n">
@@ -2884,7 +3754,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>45414</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -2902,7 +3772,7 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>100</v>
       </c>
       <c r="F7" s="4" t="n">
@@ -2914,13 +3784,13 @@
       <c r="H7" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="8" t="n">
         <v>1.3516</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>34479.25</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" s="7" t="n">
         <v>100</v>
       </c>
       <c r="M7" s="4" t="n">
@@ -2943,7 +3813,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>45453</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -2961,7 +3831,7 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>300</v>
       </c>
       <c r="F8" s="4" t="n">
@@ -2973,13 +3843,13 @@
       <c r="H8" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J8" s="8" t="n">
         <v>1.3144</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>102536.28</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" s="7" t="n">
         <v>400</v>
       </c>
       <c r="M8" s="4" t="n">
@@ -3002,7 +3872,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="6" t="n">
         <v>45471</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -3026,13 +3896,13 @@
       <c r="I9" s="4" t="n">
         <v>40.5</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="8" t="n">
         <v>1.3162</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>355.37</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="L9" s="7" t="n">
         <v>400</v>
       </c>
       <c r="M9" s="4" t="n">
@@ -3055,7 +3925,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>45471</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -3079,13 +3949,13 @@
       <c r="I10" s="4" t="n">
         <v>13.5</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="8" t="n">
         <v>1.3162</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>118.46</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="7" t="n">
         <v>400</v>
       </c>
       <c r="M10" s="4" t="n">
@@ -3108,7 +3978,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="6" t="n">
         <v>45555</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -3126,7 +3996,7 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>50</v>
       </c>
       <c r="F11" s="4" t="n">
@@ -3138,13 +4008,13 @@
       <c r="H11" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="8" t="n">
         <v>1.3711</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>15616.9</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="7" t="n">
         <v>150</v>
       </c>
       <c r="M11" s="4" t="n">
@@ -3167,7 +4037,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>45657</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -3188,13 +4058,13 @@
       <c r="G12" s="4" t="n">
         <v>310.25</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="8" t="n">
         <v>1.415</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>439</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="4" t="n">
@@ -3217,7 +4087,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="6" t="n">
         <v>45667</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -3238,13 +4108,13 @@
       <c r="G13" s="4" t="n">
         <v>1250</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="8" t="n">
         <v>1.3937</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>1742.12</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="4" t="n">
@@ -3267,7 +4137,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="6" t="n">
         <v>45702</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -3291,13 +4161,13 @@
       <c r="I14" s="4" t="n">
         <v>5.63</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="8" t="n">
         <v>1.3843</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>51.91</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="7" t="n">
         <v>150</v>
       </c>
       <c r="M14" s="4" t="n">
@@ -3320,7 +4190,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="6" t="n">
         <v>45719</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -3338,7 +4208,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>100</v>
       </c>
       <c r="F15" s="4" t="n">
@@ -3350,13 +4220,13 @@
       <c r="H15" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="8" t="n">
         <v>1.3496</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>51271.37</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="4" t="n">
@@ -3383,7 +4253,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="6" t="n">
         <v>45736</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -3401,7 +4271,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>60</v>
       </c>
       <c r="F16" s="4" t="n">
@@ -3413,13 +4283,13 @@
       <c r="H16" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="8" t="n">
         <v>1.3502</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>31203.05</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="7" t="n">
         <v>60</v>
       </c>
       <c r="M16" s="4" t="n">
@@ -3446,7 +4316,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="6" t="n">
         <v>45748</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -3464,13 +4334,13 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>100</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" s="7" t="n">
         <v>400</v>
       </c>
       <c r="M17" s="4" t="n">
@@ -3497,7 +4367,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="6" t="n">
         <v>45748</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -3518,7 +4388,7 @@
       <c r="G18" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="4" t="n">
@@ -3545,7 +4415,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="6" t="n">
         <v>45792</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -3566,13 +4436,13 @@
       <c r="G19" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="8" t="n">
         <v>1.3222</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>59.5</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" s="7" t="n">
         <v>400</v>
       </c>
       <c r="M19" s="4" t="n">
@@ -3599,7 +4469,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="6" t="n">
         <v>45835</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -3623,13 +4493,13 @@
       <c r="I20" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="8" t="n">
         <v>1.3329</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>253.25</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="L20" s="7" t="n">
         <v>400</v>
       </c>
       <c r="M20" s="4" t="n">
@@ -3652,7 +4522,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="6" t="n">
         <v>45835</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -3676,13 +4546,13 @@
       <c r="I21" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="8" t="n">
         <v>1.3329</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>253.25</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="L21" s="7" t="n">
         <v>400</v>
       </c>
       <c r="M21" s="4" t="n">
@@ -3705,7 +4575,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="6" t="n">
         <v>45853</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -3723,13 +4593,13 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>150</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L22" s="7" t="n">
         <v>300</v>
       </c>
       <c r="M22" s="4" t="n">
@@ -3756,7 +4626,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="6" t="n">
         <v>45881</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -3774,7 +4644,7 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>100</v>
       </c>
       <c r="F23" s="4" t="n">
@@ -3786,13 +4656,13 @@
       <c r="H23" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="8" t="n">
         <v>1.3697</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>15737.92</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="L23" s="7" t="n">
         <v>200</v>
       </c>
       <c r="M23" s="4" t="n">
@@ -3815,7 +4685,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="6" t="n">
         <v>45930</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -3836,7 +4706,7 @@
       <c r="G24" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="L24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="4" t="n">
@@ -3859,7 +4729,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="6" t="n">
         <v>45936</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -3877,7 +4747,7 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>150</v>
       </c>
       <c r="F25" s="4" t="n">
@@ -3889,13 +4759,13 @@
       <c r="H25" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="J25" s="8" t="n">
         <v>1.4123</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>63539.45</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="L25" s="7" t="n">
         <v>250</v>
       </c>
       <c r="M25" s="4" t="n">
@@ -3922,7 +4792,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="6" t="n">
         <v>45964</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -3943,7 +4813,7 @@
       <c r="G26" s="4" t="n">
         <v>20000</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="L26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="4" t="n">
@@ -3966,7 +4836,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="6" t="n">
         <v>45975</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -3990,13 +4860,13 @@
       <c r="I27" s="4" t="n">
         <v>15.6</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="J27" s="8" t="n">
         <v>1.4204</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>73.86</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="L27" s="7" t="n">
         <v>200</v>
       </c>
       <c r="M27" s="4" t="n">
@@ -4023,7 +4893,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="6" t="n">
         <v>46022</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -4044,13 +4914,13 @@
       <c r="G28" s="4" t="n">
         <v>412.8</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="J28" s="8" t="n">
         <v>1.3929</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>574.99</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="L28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="4" t="n">
@@ -4077,7 +4947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4138,7 +5008,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>45322</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -4146,16 +5016,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4167,7 +5037,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>45322</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -4175,16 +5045,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>135000</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>135000</v>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4196,7 +5066,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>45351</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -4204,16 +5074,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4225,7 +5095,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>45351</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -4233,16 +5103,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>135000</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>135000</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4254,7 +5124,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>45382</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -4262,16 +5132,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4283,7 +5153,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>45382</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -4291,16 +5161,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>94530.85000000001</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>94530.85000000001</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4312,7 +5182,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>45382</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -4320,16 +5190,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4341,7 +5211,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>45412</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -4349,16 +5219,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4370,7 +5240,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>45412</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -4378,16 +5248,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>94530.85000000001</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>94530.85000000001</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="F10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4399,7 +5269,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>45412</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -4407,16 +5277,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4428,7 +5298,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>45443</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -4436,16 +5306,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="F12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4457,7 +5327,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>45443</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -4465,16 +5335,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>94530.85000000001</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>94530.85000000001</v>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="F13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4486,7 +5356,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>45443</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -4494,16 +5364,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="F14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4515,7 +5385,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>45473</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -4523,16 +5393,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4544,7 +5414,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>45473</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -4552,16 +5422,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="7" t="n">
         <v>16750.4</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>16750.40000000001</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4573,7 +5443,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>45473</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -4581,16 +5451,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="F17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4602,7 +5472,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>45473</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -4610,16 +5480,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="F18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4631,7 +5501,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>45504</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -4639,16 +5509,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="F19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4660,7 +5530,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>45504</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -4668,16 +5538,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="7" t="n">
         <v>16750.4</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>16750.40000000001</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4689,7 +5559,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>45504</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -4697,16 +5567,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="F21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4718,7 +5588,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>45504</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -4726,16 +5596,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="F22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4747,7 +5617,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>45535</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -4755,16 +5625,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="F23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4776,7 +5646,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>45535</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -4784,16 +5654,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="7" t="n">
         <v>16750.4</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>16750.40000000001</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4805,7 +5675,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>45535</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -4813,16 +5683,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="F25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4834,7 +5704,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>45535</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -4842,16 +5712,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="F26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4863,7 +5733,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>45565</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -4871,16 +5741,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="F27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4892,7 +5762,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="6" t="n">
         <v>45565</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -4900,16 +5770,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="7" t="n">
         <v>28140.45</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>28140.45000000001</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4921,7 +5791,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>45565</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -4929,16 +5799,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="F29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4950,7 +5820,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>45565</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -4958,16 +5828,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="F30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4979,7 +5849,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>45596</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -4987,16 +5857,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="F31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5008,7 +5878,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="6" t="n">
         <v>45596</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -5016,16 +5886,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="7" t="n">
         <v>28140.45</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>28140.45000000001</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5037,7 +5907,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>45596</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -5045,16 +5915,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="F33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5066,7 +5936,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="6" t="n">
         <v>45596</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -5074,16 +5944,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="F34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5095,7 +5965,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="6" t="n">
         <v>45626</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -5103,16 +5973,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="F35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5124,7 +5994,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="6" t="n">
         <v>45626</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -5132,16 +6002,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="7" t="n">
         <v>28140.45</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>28140.45000000001</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5153,7 +6023,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="6" t="n">
         <v>45626</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -5161,16 +6031,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="F37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5182,7 +6052,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="6" t="n">
         <v>45626</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -5190,16 +6060,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="F38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5211,7 +6081,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="6" t="n">
         <v>45657</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -5219,16 +6089,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="F39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5240,7 +6110,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="6" t="n">
         <v>45657</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -5248,16 +6118,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="7" t="n">
         <v>28450.7</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>28450.70000000001</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5269,7 +6139,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="6" t="n">
         <v>45657</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -5277,16 +6147,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="F41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5298,7 +6168,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="6" t="n">
         <v>45657</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -5306,16 +6176,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="F42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5327,7 +6197,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="6" t="n">
         <v>45688</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -5335,16 +6205,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="F43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5356,7 +6226,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="6" t="n">
         <v>45688</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -5364,16 +6234,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="7" t="n">
         <v>27200.7</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>27200.70000000001</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G44" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5385,7 +6255,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="6" t="n">
         <v>45688</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -5393,16 +6263,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="F45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5414,7 +6284,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="6" t="n">
         <v>45688</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -5422,16 +6292,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="F46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5443,7 +6313,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="6" t="n">
         <v>45716</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -5451,16 +6321,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="F47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5472,7 +6342,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="6" t="n">
         <v>45716</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -5480,16 +6350,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="7" t="n">
         <v>27232.57</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>27232.57000000001</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G48" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5501,7 +6371,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="6" t="n">
         <v>45716</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -5509,16 +6379,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="F49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5530,7 +6400,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="6" t="n">
         <v>45716</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -5538,16 +6408,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="F50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5559,7 +6429,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="6" t="n">
         <v>45747</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -5567,16 +6437,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="F51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5588,7 +6458,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="6" t="n">
         <v>45747</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -5596,16 +6466,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="7" t="n">
         <v>42112.67</v>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" s="7" t="n">
         <v>42112.67000000001</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F52" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5617,7 +6487,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n">
+      <c r="B53" s="6" t="n">
         <v>45747</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -5625,16 +6495,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D53" s="6" t="n">
+      <c r="D53" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="E53" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="F53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5646,7 +6516,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="6" t="n">
         <v>45747</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -5654,16 +6524,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="D54" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E54" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="F54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5675,7 +6545,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n">
+      <c r="B55" s="6" t="n">
         <v>45777</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -5683,16 +6553,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="F55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5704,7 +6574,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="6" t="n">
         <v>45777</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -5712,16 +6582,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D56" s="7" t="n">
         <v>32112.67</v>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" s="7" t="n">
         <v>32112.67000000001</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F56" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G56" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5733,7 +6603,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="6" t="n">
         <v>45777</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -5741,16 +6611,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
+      <c r="F57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5762,7 +6632,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B58" s="6" t="n">
         <v>45777</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -5770,16 +6640,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D58" s="6" t="n">
+      <c r="D58" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="E58" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="F58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5791,7 +6661,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="6" t="n">
         <v>45808</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -5799,16 +6669,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="F59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5820,7 +6690,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B60" s="6" t="n">
         <v>45808</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -5828,16 +6698,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D60" s="7" t="n">
         <v>32157.67</v>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E60" s="7" t="n">
         <v>32157.67000000001</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F60" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5849,7 +6719,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n">
+      <c r="B61" s="6" t="n">
         <v>45808</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -5857,16 +6727,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E61" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="F61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5878,7 +6748,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n">
+      <c r="B62" s="6" t="n">
         <v>45808</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -5886,16 +6756,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D62" s="6" t="n">
+      <c r="D62" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="F62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5907,7 +6777,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B63" s="5" t="n">
+      <c r="B63" s="6" t="n">
         <v>45838</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -5915,16 +6785,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E63" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="F63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5936,7 +6806,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n">
+      <c r="B64" s="6" t="n">
         <v>45838</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -5944,16 +6814,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="D64" s="7" t="n">
         <v>32319.17</v>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="7" t="n">
         <v>32319.17000000001</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G64" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5965,7 +6835,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B65" s="5" t="n">
+      <c r="B65" s="6" t="n">
         <v>45838</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -5973,16 +6843,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="F65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5994,7 +6864,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="6" t="n">
         <v>45838</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -6002,16 +6872,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="F66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6023,7 +6893,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="6" t="n">
         <v>45869</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -6031,16 +6901,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E67" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="F67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
+      <c r="F67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6052,7 +6922,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n">
+      <c r="B68" s="6" t="n">
         <v>45869</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -6060,16 +6930,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="D68" s="7" t="n">
         <v>32319.17</v>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" s="7" t="n">
         <v>32319.17000000001</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F68" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="G68" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6081,7 +6951,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n">
+      <c r="B69" s="6" t="n">
         <v>45869</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -6089,16 +6959,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E69" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
+      <c r="F69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6110,7 +6980,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B70" s="5" t="n">
+      <c r="B70" s="6" t="n">
         <v>45869</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -6118,16 +6988,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D70" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E70" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F70" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
+      <c r="F70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6139,7 +7009,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B71" s="6" t="n">
         <v>45900</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -6147,16 +7017,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E71" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
+      <c r="F71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6168,7 +7038,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B72" s="5" t="n">
+      <c r="B72" s="6" t="n">
         <v>45900</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -6176,16 +7046,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" s="7" t="n">
         <v>43809.22</v>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" s="7" t="n">
         <v>43809.22000000002</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G72" s="8" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6197,7 +7067,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B73" s="5" t="n">
+      <c r="B73" s="6" t="n">
         <v>45900</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -6205,16 +7075,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E73" s="6" t="n">
+      <c r="E73" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="F73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6226,7 +7096,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B74" s="5" t="n">
+      <c r="B74" s="6" t="n">
         <v>45900</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -6234,16 +7104,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="D74" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E74" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="F74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6255,7 +7125,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B75" s="6" t="n">
         <v>45930</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -6263,16 +7133,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E75" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="F75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6284,7 +7154,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B76" s="5" t="n">
+      <c r="B76" s="6" t="n">
         <v>45930</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -6292,16 +7162,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D76" s="6" t="n">
+      <c r="D76" s="7" t="n">
         <v>93809.22</v>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="E76" s="7" t="n">
         <v>93809.22000000002</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="F76" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="G76" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6313,7 +7183,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B77" s="6" t="n">
         <v>45930</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -6321,16 +7191,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E77" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="F77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6342,7 +7212,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B78" s="6" t="n">
         <v>45930</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -6350,16 +7220,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D78" s="6" t="n">
+      <c r="D78" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E78" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="8" t="inlineStr">
+      <c r="F78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6371,7 +7241,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B79" s="6" t="n">
         <v>45961</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -6379,16 +7249,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="E79" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F79" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
+      <c r="F79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6400,7 +7270,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B80" s="5" t="n">
+      <c r="B80" s="6" t="n">
         <v>45961</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -6408,16 +7278,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="D80" s="7" t="n">
         <v>93809.22</v>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E80" s="7" t="n">
         <v>93809.22000000002</v>
       </c>
-      <c r="F80" s="6" t="n">
+      <c r="F80" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="G80" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6429,7 +7299,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B81" s="5" t="n">
+      <c r="B81" s="6" t="n">
         <v>45961</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -6437,16 +7307,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D81" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E81" s="6" t="n">
+      <c r="E81" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
+      <c r="F81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6458,7 +7328,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B82" s="5" t="n">
+      <c r="B82" s="6" t="n">
         <v>45961</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -6466,16 +7336,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D82" s="6" t="n">
+      <c r="D82" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E82" s="6" t="n">
+      <c r="E82" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="F82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6487,7 +7357,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B83" s="5" t="n">
+      <c r="B83" s="6" t="n">
         <v>45991</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -6495,16 +7365,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E83" s="6" t="n">
+      <c r="E83" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F83" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
+      <c r="F83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6516,7 +7386,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B84" s="5" t="n">
+      <c r="B84" s="6" t="n">
         <v>45991</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -6524,16 +7394,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D84" s="7" t="n">
         <v>93845.62</v>
       </c>
-      <c r="E84" s="6" t="n">
+      <c r="E84" s="7" t="n">
         <v>93845.62000000001</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="F84" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G84" s="8" t="inlineStr">
+      <c r="G84" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6545,7 +7415,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B85" s="5" t="n">
+      <c r="B85" s="6" t="n">
         <v>45991</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -6553,16 +7423,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E85" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
+      <c r="F85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6574,7 +7444,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B86" s="5" t="n">
+      <c r="B86" s="6" t="n">
         <v>45991</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -6582,16 +7452,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E86" s="6" t="n">
+      <c r="E86" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
+      <c r="F86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6603,7 +7473,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B87" s="5" t="n">
+      <c r="B87" s="6" t="n">
         <v>46022</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -6611,16 +7481,16 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E87" s="6" t="n">
+      <c r="E87" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="F87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6632,7 +7502,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B88" s="5" t="n">
+      <c r="B88" s="6" t="n">
         <v>46022</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -6640,16 +7510,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D88" s="6" t="n">
+      <c r="D88" s="7" t="n">
         <v>94258.42</v>
       </c>
-      <c r="E88" s="6" t="n">
+      <c r="E88" s="7" t="n">
         <v>94258.42000000001</v>
       </c>
-      <c r="F88" s="6" t="n">
+      <c r="F88" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G88" s="8" t="inlineStr">
+      <c r="G88" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6661,7 +7531,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B89" s="5" t="n">
+      <c r="B89" s="6" t="n">
         <v>46022</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -6669,16 +7539,16 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E89" s="6" t="n">
+      <c r="E89" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F89" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
+      <c r="F89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6690,7 +7560,7 @@
           <t>RCM-1001</t>
         </is>
       </c>
-      <c r="B90" s="5" t="n">
+      <c r="B90" s="6" t="n">
         <v>46022</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -6698,16 +7568,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="D90" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E90" s="6" t="n">
+      <c r="E90" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F90" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="F90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6719,7 +7589,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B91" s="5" t="n">
+      <c r="B91" s="6" t="n">
         <v>45322</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -6727,16 +7597,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="E91" s="6" t="n">
+      <c r="E91" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="F91" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
+      <c r="F91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6748,7 +7618,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B92" s="5" t="n">
+      <c r="B92" s="6" t="n">
         <v>45351</v>
       </c>
       <c r="C92" t="inlineStr">
@@ -6756,16 +7626,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="D92" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="E92" s="6" t="n">
+      <c r="E92" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="F92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="F92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6777,7 +7647,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B93" s="5" t="n">
+      <c r="B93" s="6" t="n">
         <v>45382</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -6785,16 +7655,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="E93" s="6" t="n">
+      <c r="E93" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="F93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
+      <c r="F93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6806,7 +7676,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B94" s="5" t="n">
+      <c r="B94" s="6" t="n">
         <v>45412</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -6814,16 +7684,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D94" s="6" t="n">
+      <c r="D94" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="E94" s="6" t="n">
+      <c r="E94" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="F94" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="8" t="inlineStr">
+      <c r="F94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6835,7 +7705,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B95" s="5" t="n">
+      <c r="B95" s="6" t="n">
         <v>45443</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -6843,16 +7713,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" s="7" t="n">
         <v>4490.05</v>
       </c>
-      <c r="E95" s="6" t="n">
+      <c r="E95" s="7" t="n">
         <v>4490.049999999999</v>
       </c>
-      <c r="F95" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
+      <c r="F95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6864,7 +7734,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B96" s="5" t="n">
+      <c r="B96" s="6" t="n">
         <v>45443</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -6872,16 +7742,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="D96" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E96" s="6" t="n">
+      <c r="E96" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F96" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="8" t="inlineStr">
+      <c r="F96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6893,7 +7763,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B97" s="5" t="n">
+      <c r="B97" s="6" t="n">
         <v>45473</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -6901,16 +7771,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="7" t="n">
         <v>4566.55</v>
       </c>
-      <c r="E97" s="6" t="n">
+      <c r="E97" s="7" t="n">
         <v>4566.549999999999</v>
       </c>
-      <c r="F97" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
+      <c r="F97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6922,7 +7792,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B98" s="5" t="n">
+      <c r="B98" s="6" t="n">
         <v>45473</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -6930,16 +7800,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D98" s="6" t="n">
+      <c r="D98" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E98" s="6" t="n">
+      <c r="E98" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
+      <c r="F98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6951,7 +7821,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B99" s="5" t="n">
+      <c r="B99" s="6" t="n">
         <v>45504</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -6959,16 +7829,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D99" s="6" t="n">
+      <c r="D99" s="7" t="n">
         <v>4566.55</v>
       </c>
-      <c r="E99" s="6" t="n">
+      <c r="E99" s="7" t="n">
         <v>4566.549999999999</v>
       </c>
-      <c r="F99" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
+      <c r="F99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6980,7 +7850,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B100" s="5" t="n">
+      <c r="B100" s="6" t="n">
         <v>45504</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -6988,16 +7858,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D100" s="6" t="n">
+      <c r="D100" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E100" s="6" t="n">
+      <c r="E100" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F100" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="8" t="inlineStr">
+      <c r="F100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7009,7 +7879,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B101" s="5" t="n">
+      <c r="B101" s="6" t="n">
         <v>45535</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -7017,16 +7887,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="7" t="n">
         <v>4566.55</v>
       </c>
-      <c r="E101" s="6" t="n">
+      <c r="E101" s="7" t="n">
         <v>4566.549999999999</v>
       </c>
-      <c r="F101" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
+      <c r="F101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7038,7 +7908,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B102" s="5" t="n">
+      <c r="B102" s="6" t="n">
         <v>45535</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -7046,16 +7916,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D102" s="6" t="n">
+      <c r="D102" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E102" s="6" t="n">
+      <c r="E102" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F102" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="8" t="inlineStr">
+      <c r="F102" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7067,7 +7937,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B103" s="5" t="n">
+      <c r="B103" s="6" t="n">
         <v>45565</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -7075,16 +7945,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="7" t="n">
         <v>4566.55</v>
       </c>
-      <c r="E103" s="6" t="n">
+      <c r="E103" s="7" t="n">
         <v>4566.549999999999</v>
       </c>
-      <c r="F103" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
+      <c r="F103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7096,7 +7966,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B104" s="5" t="n">
+      <c r="B104" s="6" t="n">
         <v>45565</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -7104,16 +7974,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D104" s="6" t="n">
+      <c r="D104" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E104" s="6" t="n">
+      <c r="E104" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F104" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="8" t="inlineStr">
+      <c r="F104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7125,7 +7995,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B105" s="5" t="n">
+      <c r="B105" s="6" t="n">
         <v>45596</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -7133,16 +8003,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="7" t="n">
         <v>4566.55</v>
       </c>
-      <c r="E105" s="6" t="n">
+      <c r="E105" s="7" t="n">
         <v>4566.549999999999</v>
       </c>
-      <c r="F105" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
+      <c r="F105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7154,7 +8024,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B106" s="5" t="n">
+      <c r="B106" s="6" t="n">
         <v>45596</v>
       </c>
       <c r="C106" t="inlineStr">
@@ -7162,16 +8032,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D106" s="6" t="n">
+      <c r="D106" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E106" s="6" t="n">
+      <c r="E106" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F106" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="8" t="inlineStr">
+      <c r="F106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7183,7 +8053,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B107" s="5" t="n">
+      <c r="B107" s="6" t="n">
         <v>45626</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -7191,16 +8061,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D107" s="7" t="n">
         <v>4566.55</v>
       </c>
-      <c r="E107" s="6" t="n">
+      <c r="E107" s="7" t="n">
         <v>4566.549999999999</v>
       </c>
-      <c r="F107" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
+      <c r="F107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7212,7 +8082,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B108" s="5" t="n">
+      <c r="B108" s="6" t="n">
         <v>45626</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -7220,16 +8090,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D108" s="6" t="n">
+      <c r="D108" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E108" s="6" t="n">
+      <c r="E108" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F108" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="8" t="inlineStr">
+      <c r="F108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7241,7 +8111,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B109" s="5" t="n">
+      <c r="B109" s="6" t="n">
         <v>45657</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -7249,16 +8119,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" s="7" t="n">
         <v>4566.55</v>
       </c>
-      <c r="E109" s="6" t="n">
+      <c r="E109" s="7" t="n">
         <v>4566.549999999999</v>
       </c>
-      <c r="F109" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
+      <c r="F109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7270,7 +8140,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B110" s="5" t="n">
+      <c r="B110" s="6" t="n">
         <v>45657</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -7278,16 +8148,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D110" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E110" s="6" t="n">
+      <c r="E110" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F110" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="8" t="inlineStr">
+      <c r="F110" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7299,7 +8169,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B111" s="5" t="n">
+      <c r="B111" s="6" t="n">
         <v>45688</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -7307,16 +8177,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" s="7" t="n">
         <v>4566.55</v>
       </c>
-      <c r="E111" s="6" t="n">
+      <c r="E111" s="7" t="n">
         <v>4566.549999999999</v>
       </c>
-      <c r="F111" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
+      <c r="F111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7328,7 +8198,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B112" s="5" t="n">
+      <c r="B112" s="6" t="n">
         <v>45688</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -7336,16 +8206,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D112" s="6" t="n">
+      <c r="D112" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E112" s="6" t="n">
+      <c r="E112" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F112" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="8" t="inlineStr">
+      <c r="F112" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7357,7 +8227,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B113" s="5" t="n">
+      <c r="B113" s="6" t="n">
         <v>45716</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -7365,16 +8235,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="7" t="n">
         <v>4566.55</v>
       </c>
-      <c r="E113" s="6" t="n">
+      <c r="E113" s="7" t="n">
         <v>4566.549999999999</v>
       </c>
-      <c r="F113" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
+      <c r="F113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7386,7 +8256,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B114" s="5" t="n">
+      <c r="B114" s="6" t="n">
         <v>45716</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -7394,16 +8264,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D114" s="6" t="n">
+      <c r="D114" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E114" s="6" t="n">
+      <c r="E114" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F114" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="8" t="inlineStr">
+      <c r="F114" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7415,7 +8285,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B115" s="5" t="n">
+      <c r="B115" s="6" t="n">
         <v>45747</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -7423,16 +8293,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="7" t="n">
         <v>4566.55</v>
       </c>
-      <c r="E115" s="6" t="n">
+      <c r="E115" s="7" t="n">
         <v>4566.549999999999</v>
       </c>
-      <c r="F115" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="8" t="inlineStr">
+      <c r="F115" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7444,7 +8314,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B116" s="5" t="n">
+      <c r="B116" s="6" t="n">
         <v>45747</v>
       </c>
       <c r="C116" t="inlineStr">
@@ -7452,16 +8322,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D116" s="6" t="n">
+      <c r="D116" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E116" s="6" t="n">
+      <c r="E116" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F116" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="8" t="inlineStr">
+      <c r="F116" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7473,7 +8343,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B117" s="5" t="n">
+      <c r="B117" s="6" t="n">
         <v>45777</v>
       </c>
       <c r="C117" t="inlineStr">
@@ -7481,16 +8351,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D117" s="6" t="n">
+      <c r="D117" s="7" t="n">
         <v>14566.55</v>
       </c>
-      <c r="E117" s="6" t="n">
+      <c r="E117" s="7" t="n">
         <v>14566.55</v>
       </c>
-      <c r="F117" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
+      <c r="F117" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7502,7 +8372,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B118" s="5" t="n">
+      <c r="B118" s="6" t="n">
         <v>45777</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -7510,16 +8380,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D118" s="6" t="n">
+      <c r="D118" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E118" s="6" t="n">
+      <c r="E118" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F118" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" s="8" t="inlineStr">
+      <c r="F118" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7531,7 +8401,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B119" s="5" t="n">
+      <c r="B119" s="6" t="n">
         <v>45808</v>
       </c>
       <c r="C119" t="inlineStr">
@@ -7539,16 +8409,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="7" t="n">
         <v>14566.55</v>
       </c>
-      <c r="E119" s="6" t="n">
+      <c r="E119" s="7" t="n">
         <v>14566.55</v>
       </c>
-      <c r="F119" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
+      <c r="F119" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7560,7 +8430,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B120" s="5" t="n">
+      <c r="B120" s="6" t="n">
         <v>45808</v>
       </c>
       <c r="C120" t="inlineStr">
@@ -7568,16 +8438,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D120" s="6" t="n">
+      <c r="D120" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E120" s="6" t="n">
+      <c r="E120" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F120" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" s="8" t="inlineStr">
+      <c r="F120" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7589,7 +8459,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B121" s="5" t="n">
+      <c r="B121" s="6" t="n">
         <v>45838</v>
       </c>
       <c r="C121" t="inlineStr">
@@ -7597,16 +8467,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" s="7" t="n">
         <v>14728.05</v>
       </c>
-      <c r="E121" s="6" t="n">
+      <c r="E121" s="7" t="n">
         <v>14728.05</v>
       </c>
-      <c r="F121" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="8" t="inlineStr">
+      <c r="F121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7618,7 +8488,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B122" s="5" t="n">
+      <c r="B122" s="6" t="n">
         <v>45838</v>
       </c>
       <c r="C122" t="inlineStr">
@@ -7626,16 +8496,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D122" s="6" t="n">
+      <c r="D122" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E122" s="6" t="n">
+      <c r="E122" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F122" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" s="8" t="inlineStr">
+      <c r="F122" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7647,7 +8517,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B123" s="5" t="n">
+      <c r="B123" s="6" t="n">
         <v>45869</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -7655,16 +8525,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D123" s="6" t="n">
+      <c r="D123" s="7" t="n">
         <v>14728.05</v>
       </c>
-      <c r="E123" s="6" t="n">
+      <c r="E123" s="7" t="n">
         <v>14728.05</v>
       </c>
-      <c r="F123" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" s="8" t="inlineStr">
+      <c r="F123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7676,7 +8546,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B124" s="5" t="n">
+      <c r="B124" s="6" t="n">
         <v>45869</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -7684,16 +8554,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D124" s="6" t="n">
+      <c r="D124" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E124" s="6" t="n">
+      <c r="E124" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F124" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="8" t="inlineStr">
+      <c r="F124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7705,7 +8575,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B125" s="5" t="n">
+      <c r="B125" s="6" t="n">
         <v>45900</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -7713,16 +8583,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D125" s="6" t="n">
+      <c r="D125" s="7" t="n">
         <v>14728.05</v>
       </c>
-      <c r="E125" s="6" t="n">
+      <c r="E125" s="7" t="n">
         <v>14728.05</v>
       </c>
-      <c r="F125" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="8" t="inlineStr">
+      <c r="F125" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7734,7 +8604,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B126" s="5" t="n">
+      <c r="B126" s="6" t="n">
         <v>45900</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -7742,16 +8612,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D126" s="6" t="n">
+      <c r="D126" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E126" s="6" t="n">
+      <c r="E126" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F126" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" s="8" t="inlineStr">
+      <c r="F126" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7763,7 +8633,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B127" s="5" t="n">
+      <c r="B127" s="6" t="n">
         <v>45930</v>
       </c>
       <c r="C127" t="inlineStr">
@@ -7771,16 +8641,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D127" s="6" t="n">
+      <c r="D127" s="7" t="n">
         <v>14728.05</v>
       </c>
-      <c r="E127" s="6" t="n">
+      <c r="E127" s="7" t="n">
         <v>14728.05</v>
       </c>
-      <c r="F127" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
+      <c r="F127" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7792,7 +8662,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B128" s="5" t="n">
+      <c r="B128" s="6" t="n">
         <v>45930</v>
       </c>
       <c r="C128" t="inlineStr">
@@ -7800,16 +8670,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D128" s="6" t="n">
+      <c r="D128" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E128" s="6" t="n">
+      <c r="E128" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F128" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="8" t="inlineStr">
+      <c r="F128" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7821,7 +8691,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B129" s="5" t="n">
+      <c r="B129" s="6" t="n">
         <v>45961</v>
       </c>
       <c r="C129" t="inlineStr">
@@ -7829,16 +8699,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D129" s="6" t="n">
+      <c r="D129" s="7" t="n">
         <v>59718.1</v>
       </c>
-      <c r="E129" s="6" t="n">
+      <c r="E129" s="7" t="n">
         <v>59718.10000000001</v>
       </c>
-      <c r="F129" s="6" t="n">
+      <c r="F129" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G129" s="8" t="inlineStr">
+      <c r="G129" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7850,7 +8720,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B130" s="5" t="n">
+      <c r="B130" s="6" t="n">
         <v>45961</v>
       </c>
       <c r="C130" t="inlineStr">
@@ -7858,16 +8728,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D130" s="6" t="n">
+      <c r="D130" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="E130" s="6" t="n">
+      <c r="E130" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="F130" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="8" t="inlineStr">
+      <c r="F130" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7879,7 +8749,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B131" s="5" t="n">
+      <c r="B131" s="6" t="n">
         <v>45991</v>
       </c>
       <c r="C131" t="inlineStr">
@@ -7887,16 +8757,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D131" s="6" t="n">
+      <c r="D131" s="7" t="n">
         <v>39718.1</v>
       </c>
-      <c r="E131" s="6" t="n">
+      <c r="E131" s="7" t="n">
         <v>39718.10000000001</v>
       </c>
-      <c r="F131" s="6" t="n">
+      <c r="F131" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G131" s="8" t="inlineStr">
+      <c r="G131" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7908,7 +8778,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B132" s="5" t="n">
+      <c r="B132" s="6" t="n">
         <v>45991</v>
       </c>
       <c r="C132" t="inlineStr">
@@ -7916,16 +8786,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D132" s="6" t="n">
+      <c r="D132" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="E132" s="6" t="n">
+      <c r="E132" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="F132" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="8" t="inlineStr">
+      <c r="F132" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7937,7 +8807,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B133" s="5" t="n">
+      <c r="B133" s="6" t="n">
         <v>46022</v>
       </c>
       <c r="C133" t="inlineStr">
@@ -7945,16 +8815,16 @@
           <t>ENCAISSE</t>
         </is>
       </c>
-      <c r="D133" s="6" t="n">
+      <c r="D133" s="7" t="n">
         <v>39718.1</v>
       </c>
-      <c r="E133" s="6" t="n">
+      <c r="E133" s="7" t="n">
         <v>39718.10000000001</v>
       </c>
-      <c r="F133" s="6" t="n">
+      <c r="F133" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="G133" s="8" t="inlineStr">
+      <c r="G133" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7966,7 +8836,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B134" s="5" t="n">
+      <c r="B134" s="6" t="n">
         <v>46022</v>
       </c>
       <c r="C134" t="inlineStr">
@@ -7974,16 +8844,16 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D134" s="6" t="n">
+      <c r="D134" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="E134" s="6" t="n">
+      <c r="E134" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="F134" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="8" t="inlineStr">
+      <c r="F134" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7995,7 +8865,7 @@
           <t>RCM-1002</t>
         </is>
       </c>
-      <c r="B135" s="5" t="n">
+      <c r="B135" s="6" t="n">
         <v>46022</v>
       </c>
       <c r="C135" t="inlineStr">
@@ -8003,542 +8873,18 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="D135" s="6" t="n">
+      <c r="D135" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E135" s="6" t="n">
+      <c r="E135" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="F135" s="6" t="n">
+      <c r="F135" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G135" s="9" t="inlineStr">
+      <c r="G135" s="10" t="inlineStr">
         <is>
           <t>ÉCART</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Année</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Élément</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Selon 1099</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Calculé (USD)</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Écart</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RCM-1001</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Dividendes bruts USD</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>318</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>318</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RCM-1001</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Impôt étranger retenu USD</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>RCM-1001</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Intérêts USD</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>310.25</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>310.25</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RCM-1001</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Produits de disposition USD</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>11390.05</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>11390.05</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RCM-1002</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Dividendes bruts USD</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RCM-1002</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Impôt étranger retenu USD</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RCM-1002</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Intérêts USD</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RCM-1002</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Produits de disposition USD</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RCM-1001</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Dividendes bruts USD</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>279.5</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>279.5</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RCM-1001</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Impôt étranger retenu USD</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RCM-1001</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Intérêts USD</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>412.8</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>412.8</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RCM-1001</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Produits de disposition USD</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>49480.1</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>49480.1</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>RCM-1002</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Dividendes bruts USD</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>190</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>190</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>RCM-1002</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Impôt étranger retenu USD</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>RCM-1002</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Intérêts USD</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>RCM-1002</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Produits de disposition USD</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>44990.05</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>44990.05</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
         </is>
       </c>
     </row>
